--- a/artfynd/A 42686-2024 artfynd.xlsx
+++ b/artfynd/A 42686-2024 artfynd.xlsx
@@ -1556,7 +1556,7 @@
         <v>121243261</v>
       </c>
       <c r="B9" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 42686-2024 artfynd.xlsx
+++ b/artfynd/A 42686-2024 artfynd.xlsx
@@ -1556,7 +1556,7 @@
         <v>121243261</v>
       </c>
       <c r="B9" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 42686-2024 artfynd.xlsx
+++ b/artfynd/A 42686-2024 artfynd.xlsx
@@ -1556,7 +1556,7 @@
         <v>121243261</v>
       </c>
       <c r="B9" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 42686-2024 artfynd.xlsx
+++ b/artfynd/A 42686-2024 artfynd.xlsx
@@ -1556,7 +1556,7 @@
         <v>121243261</v>
       </c>
       <c r="B9" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 42686-2024 artfynd.xlsx
+++ b/artfynd/A 42686-2024 artfynd.xlsx
@@ -1556,7 +1556,7 @@
         <v>121243261</v>
       </c>
       <c r="B9" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 42686-2024 artfynd.xlsx
+++ b/artfynd/A 42686-2024 artfynd.xlsx
@@ -1556,7 +1556,7 @@
         <v>121243261</v>
       </c>
       <c r="B9" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
